--- a/map/railway/edges.xlsx
+++ b/map/railway/edges.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Unida\Documents\VSC\Python\EpidemicSimulation\map\railway\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{271D7E58-2430-48D7-B85C-2CFE11DABF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3A3A793-2283-4212-A084-84EF6712E10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3F91381A-E829-4B27-8AD9-770EF5DC715D}"/>
+    <workbookView xWindow="2850" yWindow="3015" windowWidth="21600" windowHeight="11100" xr2:uid="{3F91381A-E829-4B27-8AD9-770EF5DC715D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -234,6 +234,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,13 +726,13 @@
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="5">
         <v>165</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>312</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="5">
         <v>1050</v>
       </c>
     </row>
@@ -737,13 +740,13 @@
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="5">
         <v>312</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>329</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="5">
         <v>1389</v>
       </c>
     </row>
@@ -751,13 +754,13 @@
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="5">
         <v>329</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>350</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="5">
         <v>1357</v>
       </c>
     </row>
